--- a/data/olah-data.xlsx
+++ b/data/olah-data.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marwan/Documents/BRS/PDRB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B945556-80D8-6C4E-A37D-6FC3551F4B31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32056CE0-FE2B-CA42-A030-4E571F454EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="600" windowWidth="28700" windowHeight="17400" xr2:uid="{DBD65420-4376-F945-B21D-799807FF5E50}"/>
+    <workbookView xWindow="100" yWindow="600" windowWidth="28700" windowHeight="17400" activeTab="3" xr2:uid="{DBD65420-4376-F945-B21D-799807FF5E50}"/>
   </bookViews>
   <sheets>
     <sheet name="pertumbuhan_q_to_q" sheetId="2" r:id="rId1"/>
     <sheet name="pertumbuhan_y_on_y" sheetId="3" r:id="rId2"/>
     <sheet name="pertumbuhan_c_to_c" sheetId="4" r:id="rId3"/>
+    <sheet name="distribusi" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="13">
   <si>
     <t>Uraian</t>
   </si>
@@ -86,7 +87,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -120,8 +121,20 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -134,8 +147,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -214,13 +233,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="hair">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="hair">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
@@ -240,6 +320,26 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -1049,4 +1149,102 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{923A21DB-2D8C-AE46-AC83-B4B85BB343E7}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>22.144955327724706</v>
+      </c>
+      <c r="C2">
+        <v>21.398985921874893</v>
+      </c>
+      <c r="D2">
+        <v>21.470581377978213</v>
+      </c>
+      <c r="E2">
+        <v>20.723786635685666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>17.419125447319022</v>
+      </c>
+      <c r="C3">
+        <v>18.88345207744911</v>
+      </c>
+      <c r="D3">
+        <v>18.674748090826888</v>
+      </c>
+      <c r="E3">
+        <v>19.071730427607061</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>60.43591922495628</v>
+      </c>
+      <c r="C4">
+        <v>59.717562000676004</v>
+      </c>
+      <c r="D4">
+        <v>59.854670531194913</v>
+      </c>
+      <c r="E4">
+        <v>60.204482936707279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>100</v>
+      </c>
+      <c r="C5">
+        <v>100</v>
+      </c>
+      <c r="D5">
+        <v>100.00000000000001</v>
+      </c>
+      <c r="E5">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/olah-data.xlsx
+++ b/data/olah-data.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marwan/Documents/BRS/PDRB/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32056CE0-FE2B-CA42-A030-4E571F454EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537BC1E8-79E5-6A44-9130-66CF6D527BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="600" windowWidth="28700" windowHeight="17400" activeTab="3" xr2:uid="{DBD65420-4376-F945-B21D-799807FF5E50}"/>
+    <workbookView xWindow="100" yWindow="600" windowWidth="28700" windowHeight="17400" activeTab="4" xr2:uid="{DBD65420-4376-F945-B21D-799807FF5E50}"/>
   </bookViews>
   <sheets>
     <sheet name="pertumbuhan_q_to_q" sheetId="2" r:id="rId1"/>
     <sheet name="pertumbuhan_y_on_y" sheetId="3" r:id="rId2"/>
     <sheet name="pertumbuhan_c_to_c" sheetId="4" r:id="rId3"/>
     <sheet name="distribusi" sheetId="5" r:id="rId4"/>
+    <sheet name="pdrb_adhb_adhk" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="21">
   <si>
     <t>Uraian</t>
   </si>
@@ -81,6 +82,30 @@
   </si>
   <si>
     <t>Q4 2025</t>
+  </si>
+  <si>
+    <t>Q1-adhb</t>
+  </si>
+  <si>
+    <t>Q2-adhb</t>
+  </si>
+  <si>
+    <t>Q3-adhb</t>
+  </si>
+  <si>
+    <t>Q4-adhb</t>
+  </si>
+  <si>
+    <t>Q1-adhk</t>
+  </si>
+  <si>
+    <t>Q2-adhk</t>
+  </si>
+  <si>
+    <t>Q3-adhk</t>
+  </si>
+  <si>
+    <t>Q4-adhk</t>
   </si>
 </sst>
 </file>
@@ -1247,4 +1272,162 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F996139-578B-FF4B-A4BB-385D725E1220}">
+  <dimension ref="A1:I5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="30.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>203976.3017074996</v>
+      </c>
+      <c r="C2">
+        <v>203248.55510982068</v>
+      </c>
+      <c r="D2">
+        <v>207811.49646294021</v>
+      </c>
+      <c r="E2">
+        <v>208253.83353508799</v>
+      </c>
+      <c r="F2">
+        <v>117438.70488455318</v>
+      </c>
+      <c r="G2">
+        <v>116647.19137677574</v>
+      </c>
+      <c r="H2">
+        <v>119231.58137301581</v>
+      </c>
+      <c r="I2">
+        <v>118995.86510734062</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>160446.87086249329</v>
+      </c>
+      <c r="C3">
+        <v>179355.89865049082</v>
+      </c>
+      <c r="D3">
+        <v>180750.92045731138</v>
+      </c>
+      <c r="E3">
+        <v>191652.28071098326</v>
+      </c>
+      <c r="F3">
+        <v>86592.138892428295</v>
+      </c>
+      <c r="G3">
+        <v>96281.01939705103</v>
+      </c>
+      <c r="H3">
+        <v>96822.693249354343</v>
+      </c>
+      <c r="I3">
+        <v>102488.51335112307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>556672.84541171172</v>
+      </c>
+      <c r="C4">
+        <v>567200.15778463066</v>
+      </c>
+      <c r="D4">
+        <v>579327.05381427996</v>
+      </c>
+      <c r="E4">
+        <v>604996.30632065015</v>
+      </c>
+      <c r="F4">
+        <v>305213.11407383246</v>
+      </c>
+      <c r="G4">
+        <v>310035.94619361404</v>
+      </c>
+      <c r="H4">
+        <v>315114.81494311302</v>
+      </c>
+      <c r="I4">
+        <v>327069.65244625811</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>921096.01798170456</v>
+      </c>
+      <c r="C5">
+        <v>949804.61154494213</v>
+      </c>
+      <c r="D5">
+        <v>967889.47073453153</v>
+      </c>
+      <c r="E5">
+        <v>1004902.4205667214</v>
+      </c>
+      <c r="F5">
+        <v>509243.95785081392</v>
+      </c>
+      <c r="G5">
+        <v>522964.15696744079</v>
+      </c>
+      <c r="H5">
+        <v>531169.08956548315</v>
+      </c>
+      <c r="I5">
+        <v>548554.03090472182</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/olah-data.xlsx
+++ b/data/olah-data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537BC1E8-79E5-6A44-9130-66CF6D527BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="100" yWindow="600" windowWidth="28700" windowHeight="17400" activeTab="4" xr2:uid="{DBD65420-4376-F945-B21D-799807FF5E50}"/>
+    <workbookView xWindow="100" yWindow="600" windowWidth="28700" windowHeight="17400" activeTab="3" xr2:uid="{DBD65420-4376-F945-B21D-799807FF5E50}"/>
   </bookViews>
   <sheets>
     <sheet name="pertumbuhan_q_to_q" sheetId="2" r:id="rId1"/>
